--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9769,0.0097,0.0082,0.0009</t>
-  </si>
-  <si>
-    <t>0.8255,0.0615,0.0517,0.0274</t>
-  </si>
-  <si>
-    <t>0.6792,0.2873,0.0268,0.0048</t>
-  </si>
-  <si>
-    <t>0.9599,0.0192,0.0098,0.0021</t>
-  </si>
-  <si>
-    <t>0.8352,0.0964,0.0081,0.0135</t>
-  </si>
-  <si>
-    <t>0.8692,0.1027,0.0055,0.0051</t>
-  </si>
-  <si>
-    <t>0.8860,0.0491,0.0041,0.0074</t>
-  </si>
-  <si>
-    <t>0.7846,0.0782,0.0077,0.0191</t>
-  </si>
-  <si>
-    <t>0.5967,0.2059,0.0071,0.0138</t>
-  </si>
-  <si>
-    <t>0.9262,0.0805,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.9594,0.0167,0.0009,0.0022</t>
-  </si>
-  <si>
-    <t>0.9006,0.0579,0.0060,0.0112</t>
-  </si>
-  <si>
-    <t>0.9807,0.0129,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.9262,0.0894,0.0066,0.0004</t>
-  </si>
-  <si>
-    <t>0.9536,0.0277,0.0145,0.0002</t>
-  </si>
-  <si>
-    <t>0.9871,0.0047,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.9668,0.0158,0.0076,0.0007</t>
-  </si>
-  <si>
-    <t>0.6518,0.4593,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.8582,0.2488,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9117,0.0669,0.0170,0.0029</t>
-  </si>
-  <si>
-    <t>0.6246,0.5193,0.0071,0.0004</t>
-  </si>
-  <si>
-    <t>0.8184,0.2063,0.0069,0.0012</t>
-  </si>
-  <si>
-    <t>0.9796,0.0061,0.0095,0.0012</t>
-  </si>
-  <si>
-    <t>0.9526,0.0138,0.0348,0.0010</t>
-  </si>
-  <si>
-    <t>0.9149,0.0199,0.0775,0.0021</t>
-  </si>
-  <si>
-    <t>0.9262,0.0271,0.0363,0.0003</t>
-  </si>
-  <si>
-    <t>0.9858,0.0028,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.9623,0.0097,0.0158,0.0027</t>
-  </si>
-  <si>
-    <t>0.9518,0.0028,0.0901,0.0005</t>
-  </si>
-  <si>
-    <t>0.8610,0.1936,0.0065,0.0002</t>
-  </si>
-  <si>
-    <t>0.9571,0.0327,0.0074,0.0005</t>
-  </si>
-  <si>
-    <t>0.4686,0.1509,0.5411,0.0106</t>
-  </si>
-  <si>
-    <t>0.9559,0.0416,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.8840,0.1334,0.0050,0.0018</t>
-  </si>
-  <si>
-    <t>0.9315,0.1039,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.8997,0.1150,0.0051,0.0009</t>
-  </si>
-  <si>
-    <t>0.9098,0.0777,0.0097,0.0019</t>
-  </si>
-  <si>
-    <t>0.2900,0.6338,0.3071,0.0076</t>
-  </si>
-  <si>
-    <t>0.8910,0.0265,0.0980,0.0060</t>
-  </si>
-  <si>
-    <t>0.8843,0.0422,0.0664,0.0037</t>
-  </si>
-  <si>
-    <t>0.9847,0.0024,0.0112,0.0010</t>
-  </si>
-  <si>
-    <t>0.8503,0.0626,0.0724,0.0016</t>
-  </si>
-  <si>
-    <t>0.3899,0.4875,0.1726,0.0016</t>
-  </si>
-  <si>
-    <t>0.8536,0.0358,0.1400,0.0023</t>
-  </si>
-  <si>
-    <t>0.9612,0.0457,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.8957,0.1173,0.0042,0.0004</t>
-  </si>
-  <si>
-    <t>0.5087,0.6508,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.7188,0.4073,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.5904,0.0402,0.5926,0.0025</t>
-  </si>
-  <si>
-    <t>0.4012,0.2806,0.3983,0.0015</t>
-  </si>
-  <si>
-    <t>0.9426,0.0102,0.0619,0.0005</t>
-  </si>
-  <si>
-    <t>0.9030,0.0144,0.1206,0.0016</t>
-  </si>
-  <si>
-    <t>0.3297,0.1433,0.5290,0.0006</t>
-  </si>
-  <si>
-    <t>0.9201,0.0091,0.1079,0.0003</t>
-  </si>
-  <si>
-    <t>0.8403,0.1519,0.0177,0.0053</t>
-  </si>
-  <si>
-    <t>0.9141,0.0738,0.0064,0.0020</t>
-  </si>
-  <si>
-    <t>0.8202,0.0857,0.0287,0.0290</t>
-  </si>
-  <si>
-    <t>0.2917,0.5738,0.3263,0.0088</t>
-  </si>
-  <si>
-    <t>0.9388,0.0286,0.0077,0.0075</t>
-  </si>
-  <si>
-    <t>0.8999,0.0765,0.0065,0.0044</t>
-  </si>
-  <si>
-    <t>0.8778,0.0881,0.0111,0.0070</t>
-  </si>
-  <si>
-    <t>0.0113,0.9156,0.8629,0.0012</t>
-  </si>
-  <si>
-    <t>0.7547,0.0318,0.3875,0.0020</t>
-  </si>
-  <si>
-    <t>0.8081,0.0309,0.2615,0.0020</t>
-  </si>
-  <si>
-    <t>0.1976,0.6714,0.3402,0.0015</t>
-  </si>
-  <si>
-    <t>0.1962,0.1205,0.8125,0.0006</t>
-  </si>
-  <si>
-    <t>0.5892,0.5628,0.0109,0.0002</t>
-  </si>
-  <si>
-    <t>0.0745,0.9664,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.8859,0.1190,0.0132,0.0011</t>
-  </si>
-  <si>
-    <t>0.9587,0.0275,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.0072,0.9149,0.7218,0.0023</t>
-  </si>
-  <si>
-    <t>0.7111,0.1610,0.1167,0.0007</t>
-  </si>
-  <si>
-    <t>0.5965,0.3271,0.0873,0.0005</t>
-  </si>
-  <si>
-    <t>0.3040,0.7201,0.0453,0.0002</t>
-  </si>
-  <si>
-    <t>0.1654,0.6436,0.3425,0.0006</t>
-  </si>
-  <si>
-    <t>0.9705,0.0053,0.0204,0.0016</t>
-  </si>
-  <si>
-    <t>0.9088,0.0110,0.0039,0.0292</t>
-  </si>
-  <si>
-    <t>0.9362,0.0111,0.0129,0.0228</t>
-  </si>
-  <si>
-    <t>0.9421,0.0216,0.0196,0.0049</t>
-  </si>
-  <si>
-    <t>0.8213,0.0127,0.0132,0.1243</t>
-  </si>
-  <si>
-    <t>0.9782,0.0028,0.0107,0.0025</t>
-  </si>
-  <si>
-    <t>0.0445,0.8928,0.4653,0.0015</t>
-  </si>
-  <si>
-    <t>0.0389,0.8878,0.6663,0.0027</t>
-  </si>
-  <si>
-    <t>0.6359,0.2145,0.1574,0.0034</t>
-  </si>
-  <si>
-    <t>0.2108,0.3483,0.6313,0.0016</t>
-  </si>
-  <si>
-    <t>0.1352,0.7141,0.3175,0.0012</t>
-  </si>
-  <si>
-    <t>0.3058,0.6432,0.1915,0.0026</t>
-  </si>
-  <si>
-    <t>0.8729,0.0941,0.0081,0.0036</t>
-  </si>
-  <si>
-    <t>0.8966,0.0608,0.0128,0.0127</t>
-  </si>
-  <si>
-    <t>0.7347,0.2290,0.0110,0.0072</t>
-  </si>
-  <si>
-    <t>0.6741,0.3165,0.0131,0.0049</t>
-  </si>
-  <si>
-    <t>0.6147,0.2654,0.0283,0.0204</t>
-  </si>
-  <si>
-    <t>0.9059,0.0556,0.0053,0.0052</t>
-  </si>
-  <si>
-    <t>0.8464,0.1095,0.0081,0.0036</t>
-  </si>
-  <si>
-    <t>0.8948,0.0489,0.0153,0.0188</t>
-  </si>
-  <si>
-    <t>0.8706,0.0608,0.0134,0.0242</t>
-  </si>
-  <si>
-    <t>0.9142,0.0714,0.0053,0.0024</t>
-  </si>
-  <si>
-    <t>0.7844,0.0965,0.0127,0.0223</t>
-  </si>
-  <si>
-    <t>0.8060,0.1339,0.0155,0.0117</t>
-  </si>
-  <si>
-    <t>0.8087,0.1223,0.0327,0.0230</t>
-  </si>
-  <si>
-    <t>0.7741,0.2396,0.0131,0.0037</t>
-  </si>
-  <si>
-    <t>0.9495,0.0337,0.0017,0.0015</t>
-  </si>
-  <si>
-    <t>0.8588,0.0967,0.0130,0.0107</t>
-  </si>
-  <si>
-    <t>0.7031,0.0092,0.4617,0.0018</t>
-  </si>
-  <si>
-    <t>0.8560,0.0460,0.0918,0.0008</t>
-  </si>
-  <si>
-    <t>0.9855,0.0014,0.0114,0.0006</t>
-  </si>
-  <si>
-    <t>0.9863,0.0039,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.2163,0.8530,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.1359,0.8755,0.0096,0.0048</t>
-  </si>
-  <si>
-    <t>0.7564,0.2912,0.0121,0.0014</t>
-  </si>
-  <si>
-    <t>0.2929,0.8115,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.0939,0.9146,0.0103,0.0039</t>
-  </si>
-  <si>
-    <t>0.0135,0.9855,0.0042,0.0014</t>
-  </si>
-  <si>
-    <t>0.2077,0.7241,0.0146,0.0160</t>
-  </si>
-  <si>
-    <t>0.9830,0.0088,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9610,0.0281,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.9361,0.0378,0.0133,0.0013</t>
-  </si>
-  <si>
-    <t>0.9446,0.0271,0.0330,0.0009</t>
-  </si>
-  <si>
-    <t>0.9291,0.0448,0.0098,0.0023</t>
-  </si>
-  <si>
-    <t>0.6733,0.3928,0.0127,0.0008</t>
-  </si>
-  <si>
-    <t>0.5256,0.6553,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.4818,0.4991,0.0163,0.0057</t>
-  </si>
-  <si>
-    <t>0.2063,0.8034,0.0898,0.0021</t>
-  </si>
-  <si>
-    <t>0.9357,0.0713,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.7600,0.3143,0.0129,0.0012</t>
-  </si>
-  <si>
-    <t>0.8145,0.1678,0.0096,0.0034</t>
-  </si>
-  <si>
-    <t>0.9323,0.0330,0.0133,0.0079</t>
-  </si>
-  <si>
-    <t>0.8505,0.1329,0.0107,0.0058</t>
-  </si>
-  <si>
-    <t>0.5323,0.2694,0.0202,0.0458</t>
-  </si>
-  <si>
-    <t>0.9351,0.0587,0.0068,0.0022</t>
-  </si>
-  <si>
-    <t>0.8731,0.0915,0.0127,0.0103</t>
-  </si>
-  <si>
-    <t>0.9356,0.0635,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.8323,0.1416,0.0042,0.0033</t>
-  </si>
-  <si>
-    <t>0.8703,0.0931,0.0163,0.0145</t>
-  </si>
-  <si>
-    <t>0.3956,0.3976,0.2565,0.0036</t>
-  </si>
-  <si>
-    <t>0.0900,0.6856,0.5704,0.0017</t>
-  </si>
-  <si>
-    <t>0.4130,0.1714,0.4204,0.0030</t>
-  </si>
-  <si>
-    <t>0.7385,0.0947,0.2075,0.0015</t>
-  </si>
-  <si>
-    <t>0.9552,0.0159,0.0157,0.0036</t>
-  </si>
-  <si>
-    <t>0.9781,0.0048,0.0086,0.0007</t>
-  </si>
-  <si>
-    <t>0.9855,0.0029,0.0129,0.0002</t>
-  </si>
-  <si>
-    <t>0.9793,0.0075,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.9482,0.0174,0.0170,0.0049</t>
-  </si>
-  <si>
-    <t>0.8737,0.0034,0.0070,0.0761</t>
-  </si>
-  <si>
-    <t>0.9498,0.0060,0.0218,0.0115</t>
-  </si>
-  <si>
-    <t>0.9755,0.0052,0.0094,0.0040</t>
-  </si>
-  <si>
-    <t>0.0584,0.8906,0.3816,0.0093</t>
-  </si>
-  <si>
-    <t>0.5838,0.3278,0.0122,0.0113</t>
-  </si>
-  <si>
-    <t>0.8204,0.1455,0.0214,0.0072</t>
-  </si>
-  <si>
-    <t>0.9776,0.0150,0.0047,0.0020</t>
-  </si>
-  <si>
-    <t>0.6986,0.2140,0.0210,0.0142</t>
-  </si>
-  <si>
-    <t>0.9011,0.0725,0.0118,0.0056</t>
-  </si>
-  <si>
-    <t>0.9529,0.0149,0.0025,0.0027</t>
-  </si>
-  <si>
-    <t>0.9297,0.0273,0.0132,0.0104</t>
-  </si>
-  <si>
-    <t>0.0799,0.7948,0.5549,0.0120</t>
-  </si>
-  <si>
-    <t>0.9052,0.0622,0.0070,0.0052</t>
-  </si>
-  <si>
-    <t>0.9269,0.0449,0.0198,0.0023</t>
-  </si>
-  <si>
-    <t>0.9311,0.0545,0.0102,0.0019</t>
-  </si>
-  <si>
-    <t>0.7760,0.2435,0.0138,0.0024</t>
-  </si>
-  <si>
-    <t>0.9913,0.0051,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.8873,0.1295,0.0049,0.0003</t>
-  </si>
-  <si>
-    <t>0.9325,0.0277,0.0115,0.0046</t>
-  </si>
-  <si>
-    <t>0.9589,0.0237,0.0071,0.0014</t>
-  </si>
-  <si>
-    <t>0.8886,0.0640,0.0095,0.0080</t>
-  </si>
-  <si>
-    <t>0.8003,0.1576,0.0128,0.0100</t>
-  </si>
-  <si>
-    <t>0.9426,0.0582,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.8651,0.0540,0.0104,0.0126</t>
-  </si>
-  <si>
-    <t>0.9524,0.0404,0.0024,0.0013</t>
-  </si>
-  <si>
-    <t>0.9221,0.0467,0.0189,0.0059</t>
-  </si>
-  <si>
-    <t>0.8805,0.0795,0.0132,0.0081</t>
-  </si>
-  <si>
-    <t>0.9271,0.0380,0.0090,0.0061</t>
-  </si>
-  <si>
-    <t>0.5752,0.5815,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.6696,0.3301,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.9043,0.0638,0.0070,0.0032</t>
-  </si>
-  <si>
-    <t>0.9549,0.0386,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.9212,0.0703,0.0090,0.0029</t>
-  </si>
-  <si>
-    <t>0.9351,0.0354,0.0051,0.0032</t>
-  </si>
-  <si>
-    <t>0.8996,0.1421,0.0030,0.0006</t>
-  </si>
-  <si>
-    <t>0.8270,0.2383,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.0151,0.8773,0.8007,0.0016</t>
-  </si>
-  <si>
-    <t>0.8825,0.0817,0.0049,0.0050</t>
-  </si>
-  <si>
-    <t>0.9395,0.0125,0.0535,0.0004</t>
-  </si>
-  <si>
-    <t>0.8154,0.1155,0.0544,0.0016</t>
-  </si>
-  <si>
-    <t>0.9482,0.0099,0.0517,0.0008</t>
-  </si>
-  <si>
-    <t>0.7377,0.0365,0.4196,0.0029</t>
-  </si>
-  <si>
-    <t>0.8409,0.1122,0.0228,0.0010</t>
-  </si>
-  <si>
-    <t>0.9339,0.0230,0.0255,0.0001</t>
-  </si>
-  <si>
-    <t>0.8388,0.0398,0.1400,0.0014</t>
-  </si>
-  <si>
-    <t>0.9355,0.0540,0.0058,0.0013</t>
-  </si>
-  <si>
-    <t>0.9109,0.0517,0.0219,0.0008</t>
-  </si>
-  <si>
-    <t>0.9810,0.0113,0.0033,0.0007</t>
-  </si>
-  <si>
-    <t>0.9678,0.0294,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.7789,0.1658,0.0650,0.0062</t>
-  </si>
-  <si>
-    <t>0.9791,0.0094,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.9892,0.0027,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.9514,0.0359,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.9049,0.0757,0.0037,0.0022</t>
-  </si>
-  <si>
-    <t>0.8648,0.1515,0.0050,0.0019</t>
-  </si>
-  <si>
-    <t>0.8284,0.1706,0.0051,0.0018</t>
-  </si>
-  <si>
-    <t>0.8932,0.1096,0.0075,0.0032</t>
-  </si>
-  <si>
-    <t>0.8937,0.0832,0.0053,0.0039</t>
-  </si>
-  <si>
-    <t>0.8956,0.0782,0.0058,0.0020</t>
-  </si>
-  <si>
-    <t>0.9864,0.0053,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9603,0.0116,0.0162,0.0013</t>
-  </si>
-  <si>
-    <t>0.9530,0.0132,0.0353,0.0007</t>
-  </si>
-  <si>
-    <t>0.9712,0.0069,0.0127,0.0006</t>
-  </si>
-  <si>
-    <t>0.3573,0.1277,0.4500,0.0029</t>
-  </si>
-  <si>
-    <t>0.9136,0.0246,0.0731,0.0016</t>
-  </si>
-  <si>
-    <t>0.8642,0.0683,0.0570,0.0041</t>
-  </si>
-  <si>
-    <t>0.6736,0.1716,0.1550,0.0014</t>
-  </si>
-  <si>
-    <t>0.8878,0.0391,0.0934,0.0031</t>
-  </si>
-  <si>
-    <t>0.8470,0.0499,0.0089,0.0219</t>
-  </si>
-  <si>
-    <t>0.4676,0.2630,0.0203,0.0685</t>
-  </si>
-  <si>
-    <t>0.7641,0.0930,0.0067,0.0184</t>
-  </si>
-  <si>
-    <t>0.8270,0.1324,0.0129,0.0090</t>
-  </si>
-  <si>
-    <t>0.5892,0.2080,0.0098,0.0272</t>
-  </si>
-  <si>
-    <t>0.9031,0.0673,0.0171,0.0054</t>
-  </si>
-  <si>
-    <t>0.9277,0.0397,0.0010,0.0023</t>
-  </si>
-  <si>
-    <t>0.6786,0.1509,0.0065,0.0092</t>
-  </si>
-  <si>
-    <t>0.9402,0.0291,0.0279,0.0010</t>
-  </si>
-  <si>
-    <t>0.7707,0.1510,0.0022,0.0036</t>
-  </si>
-  <si>
-    <t>0.9770,0.0152,0.0042,0.0007</t>
-  </si>
-  <si>
-    <t>0.9496,0.0086,0.0563,0.0005</t>
-  </si>
-  <si>
-    <t>0.6351,0.2660,0.1612,0.0059</t>
-  </si>
-  <si>
-    <t>0.9714,0.0110,0.0123,0.0002</t>
-  </si>
-  <si>
-    <t>0.0931,0.2450,0.8414,0.0008</t>
-  </si>
-  <si>
-    <t>0.9929,0.0008,0.0058,0.0001</t>
-  </si>
-  <si>
-    <t>0.3833,0.0624,0.7253,0.0022</t>
-  </si>
-  <si>
-    <t>0.8901,0.0444,0.0520,0.0007</t>
-  </si>
-  <si>
-    <t>0.8999,0.0492,0.0294,0.0007</t>
-  </si>
-  <si>
-    <t>0.9678,0.0098,0.0125,0.0010</t>
-  </si>
-  <si>
-    <t>0.9904,0.0012,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.9734,0.0034,0.0125,0.0022</t>
-  </si>
-  <si>
-    <t>0.6995,0.2835,0.0190,0.0077</t>
-  </si>
-  <si>
-    <t>0.8429,0.0371,0.0077,0.0297</t>
-  </si>
-  <si>
-    <t>0.9494,0.0294,0.0020,0.0020</t>
-  </si>
-  <si>
-    <t>0.9229,0.0557,0.0083,0.0038</t>
-  </si>
-  <si>
-    <t>0.7960,0.1503,0.0150,0.0137</t>
-  </si>
-  <si>
-    <t>0.6595,0.2806,0.0222,0.0138</t>
-  </si>
-  <si>
-    <t>0.8701,0.0419,0.0074,0.0156</t>
-  </si>
-  <si>
-    <t>0.6906,0.1900,0.0114,0.0116</t>
-  </si>
-  <si>
-    <t>0.8858,0.0574,0.0395,0.0007</t>
-  </si>
-  <si>
-    <t>0.9570,0.0082,0.0470,0.0007</t>
-  </si>
-  <si>
-    <t>0.9401,0.0046,0.1102,0.0003</t>
-  </si>
-  <si>
-    <t>0.9582,0.0136,0.0190,0.0007</t>
-  </si>
-  <si>
-    <t>0.8481,0.0197,0.1754,0.0003</t>
-  </si>
-  <si>
-    <t>0.9619,0.0052,0.0358,0.0015</t>
-  </si>
-  <si>
-    <t>0.9577,0.0101,0.0251,0.0008</t>
-  </si>
-  <si>
-    <t>0.6077,0.2455,0.1772,0.0063</t>
-  </si>
-  <si>
-    <t>0.9220,0.0194,0.0152,0.0126</t>
-  </si>
-  <si>
-    <t>0.9611,0.0089,0.0227,0.0032</t>
-  </si>
-  <si>
-    <t>0.9657,0.0063,0.0030,0.0064</t>
-  </si>
-  <si>
-    <t>0.9217,0.0138,0.0426,0.0111</t>
-  </si>
-  <si>
-    <t>0.8515,0.0070,0.0193,0.0783</t>
-  </si>
-  <si>
-    <t>0.8929,0.0572,0.0193,0.0054</t>
+    <t>0.9708,0.0107,0.0019,0.0106</t>
+  </si>
+  <si>
+    <t>0.0096,0.0014,0.0010,0.9949</t>
+  </si>
+  <si>
+    <t>0.8631,0.0037,0.0033,0.1655</t>
+  </si>
+  <si>
+    <t>0.0047,0.0006,0.0024,0.9960</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0011,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9950,0.0022,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9944,0.0042,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9944,0.0005,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.9879,0.0060,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.6121,0.0335,0.4444,0.0065</t>
+  </si>
+  <si>
+    <t>0.6546,0.0225,0.4281,0.0038</t>
+  </si>
+  <si>
+    <t>0.2272,0.1215,0.7337,0.0025</t>
+  </si>
+  <si>
+    <t>0.2631,0.0192,0.7467,0.0017</t>
+  </si>
+  <si>
+    <t>0.9713,0.0033,0.0337,0.0009</t>
+  </si>
+  <si>
+    <t>0.0085,0.9932,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0124,0.9839,0.0035,0.0013</t>
+  </si>
+  <si>
+    <t>0.1338,0.9125,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.0319,0.9761,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.0042,0.9936,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.8111,0.0135,0.2604,0.0153</t>
+  </si>
+  <si>
+    <t>0.8258,0.0076,0.2014,0.0124</t>
+  </si>
+  <si>
+    <t>0.0344,0.1316,0.8996,0.0637</t>
+  </si>
+  <si>
+    <t>0.0759,0.0112,0.9190,0.0124</t>
+  </si>
+  <si>
+    <t>0.1799,0.0191,0.8693,0.0060</t>
+  </si>
+  <si>
+    <t>0.1628,0.0027,0.8824,0.0068</t>
+  </si>
+  <si>
+    <t>0.0083,0.0029,0.9805,0.0143</t>
+  </si>
+  <si>
+    <t>0.8175,0.3624,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.8341,0.0552,0.1122,0.0237</t>
+  </si>
+  <si>
+    <t>0.0028,0.0051,0.9913,0.0067</t>
+  </si>
+  <si>
+    <t>0.0944,0.7729,0.0698,0.0069</t>
+  </si>
+  <si>
+    <t>0.8797,0.1183,0.0184,0.0148</t>
+  </si>
+  <si>
+    <t>0.9006,0.0623,0.0269,0.0299</t>
+  </si>
+  <si>
+    <t>0.8431,0.2329,0.0067,0.0008</t>
+  </si>
+  <si>
+    <t>0.0021,0.9931,0.1522,0.0002</t>
+  </si>
+  <si>
+    <t>0.0256,0.7899,0.0800,0.0682</t>
+  </si>
+  <si>
+    <t>0.0601,0.0798,0.9190,0.0244</t>
+  </si>
+  <si>
+    <t>0.2447,0.0189,0.8359,0.0020</t>
+  </si>
+  <si>
+    <t>0.2494,0.0116,0.6378,0.1018</t>
+  </si>
+  <si>
+    <t>0.0258,0.0647,0.9693,0.0017</t>
+  </si>
+  <si>
+    <t>0.0333,0.8262,0.0979,0.0108</t>
+  </si>
+  <si>
+    <t>0.0075,0.0868,0.9705,0.0064</t>
+  </si>
+  <si>
+    <t>0.7600,0.0858,0.0378,0.1720</t>
+  </si>
+  <si>
+    <t>0.0030,0.9901,0.0067,0.0131</t>
+  </si>
+  <si>
+    <t>0.0027,0.9901,0.0204,0.0009</t>
+  </si>
+  <si>
+    <t>0.0035,0.9920,0.0183,0.0005</t>
+  </si>
+  <si>
+    <t>0.0376,0.0109,0.9565,0.0048</t>
+  </si>
+  <si>
+    <t>0.0412,0.2917,0.9159,0.0099</t>
+  </si>
+  <si>
+    <t>0.1904,0.0066,0.8723,0.0014</t>
+  </si>
+  <si>
+    <t>0.0072,0.0017,0.9650,0.0410</t>
+  </si>
+  <si>
+    <t>0.0111,0.0532,0.9807,0.0022</t>
+  </si>
+  <si>
+    <t>0.0020,0.1156,0.9874,0.0023</t>
+  </si>
+  <si>
+    <t>0.9819,0.0267,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0013,0.0019,0.0018</t>
+  </si>
+  <si>
+    <t>0.9703,0.0218,0.0028,0.0052</t>
+  </si>
+  <si>
+    <t>0.0223,0.1459,0.9532,0.0141</t>
+  </si>
+  <si>
+    <t>0.9904,0.0020,0.0035,0.0018</t>
+  </si>
+  <si>
+    <t>0.9969,0.0017,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9874,0.0203,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0039,0.7833,0.9551,0.0010</t>
+  </si>
+  <si>
+    <t>0.0319,0.1035,0.9532,0.0071</t>
+  </si>
+  <si>
+    <t>0.0044,0.0067,0.9922,0.0008</t>
+  </si>
+  <si>
+    <t>0.0038,0.9037,0.7428,0.0004</t>
+  </si>
+  <si>
+    <t>0.0047,0.0082,0.9885,0.0038</t>
+  </si>
+  <si>
+    <t>0.2271,0.8466,0.0075,0.0015</t>
+  </si>
+  <si>
+    <t>0.0176,0.9929,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3011,0.1069,0.7554,0.0156</t>
+  </si>
+  <si>
+    <t>0.9625,0.0129,0.0273,0.0047</t>
+  </si>
+  <si>
+    <t>0.0077,0.0095,0.9871,0.0024</t>
+  </si>
+  <si>
+    <t>0.0084,0.8844,0.4825,0.0014</t>
+  </si>
+  <si>
+    <t>0.0112,0.7962,0.8360,0.0032</t>
+  </si>
+  <si>
+    <t>0.0061,0.9779,0.0365,0.0068</t>
+  </si>
+  <si>
+    <t>0.0023,0.9489,0.7461,0.0009</t>
+  </si>
+  <si>
+    <t>0.0075,0.0014,0.0165,0.9900</t>
+  </si>
+  <si>
+    <t>0.0420,0.0005,0.0006,0.9870</t>
+  </si>
+  <si>
+    <t>0.0026,0.0033,0.0004,0.9978</t>
+  </si>
+  <si>
+    <t>0.0117,0.0014,0.0049,0.9916</t>
+  </si>
+  <si>
+    <t>0.0019,0.0060,0.0029,0.9964</t>
+  </si>
+  <si>
+    <t>0.0415,0.0054,0.0042,0.9790</t>
+  </si>
+  <si>
+    <t>0.0002,0.9775,0.9630,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.8907,0.9561,0.0009</t>
+  </si>
+  <si>
+    <t>0.0175,0.7495,0.7977,0.0083</t>
+  </si>
+  <si>
+    <t>0.0064,0.5757,0.8994,0.0017</t>
+  </si>
+  <si>
+    <t>0.0019,0.6767,0.9700,0.0005</t>
+  </si>
+  <si>
+    <t>0.0065,0.6463,0.7817,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9946,0.0041,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0021,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9842,0.0069,0.0015,0.0036</t>
+  </si>
+  <si>
+    <t>0.9959,0.0021,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0019,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9934,0.0034,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.0834,0.0026,0.9660,0.0006</t>
+  </si>
+  <si>
+    <t>0.0058,0.0114,0.9837,0.0019</t>
+  </si>
+  <si>
+    <t>0.8549,0.0041,0.1591,0.0062</t>
+  </si>
+  <si>
+    <t>0.0099,0.0091,0.9771,0.0076</t>
+  </si>
+  <si>
+    <t>0.2081,0.8739,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.0370,0.9764,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.0226,0.9748,0.0003,0.0054</t>
+  </si>
+  <si>
+    <t>0.0080,0.9911,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0244,0.9789,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.0340,0.9680,0.0043,0.0014</t>
+  </si>
+  <si>
+    <t>0.9542,0.0916,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8372,0.0530,0.0952,0.0304</t>
+  </si>
+  <si>
+    <t>0.1312,0.0171,0.8790,0.0095</t>
+  </si>
+  <si>
+    <t>0.3296,0.2993,0.4196,0.0496</t>
+  </si>
+  <si>
+    <t>0.8015,0.0055,0.3247,0.0011</t>
+  </si>
+  <si>
+    <t>0.0966,0.0705,0.4241,0.6535</t>
+  </si>
+  <si>
+    <t>0.0039,0.9910,0.0101,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.9969,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.0117,0.9707,0.0401,0.0288</t>
+  </si>
+  <si>
+    <t>0.0047,0.8704,0.7121,0.0037</t>
+  </si>
+  <si>
+    <t>0.0042,0.9946,0.0096,0.0000</t>
+  </si>
+  <si>
+    <t>0.7017,0.4549,0.0068,0.0005</t>
+  </si>
+  <si>
+    <t>0.9585,0.0804,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.9776,0.0231,0.0054,0.0020</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0029,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0010,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9947,0.0011,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.0049,0.8147,0.8094,0.0031</t>
+  </si>
+  <si>
+    <t>0.0046,0.3501,0.9580,0.0011</t>
+  </si>
+  <si>
+    <t>0.0299,0.1024,0.9184,0.0016</t>
+  </si>
+  <si>
+    <t>0.0275,0.1413,0.9524,0.0006</t>
+  </si>
+  <si>
+    <t>0.9902,0.0018,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.5928,0.0092,0.4675,0.0132</t>
+  </si>
+  <si>
+    <t>0.9060,0.0016,0.2321,0.0010</t>
+  </si>
+  <si>
+    <t>0.8330,0.0247,0.1922,0.0123</t>
+  </si>
+  <si>
+    <t>0.0541,0.0005,0.0028,0.9754</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.0006,0.9996</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.0006,0.9993</t>
+  </si>
+  <si>
+    <t>0.0048,0.0003,0.0005,0.9976</t>
+  </si>
+  <si>
+    <t>0.0020,0.9391,0.3211,0.0038</t>
+  </si>
+  <si>
+    <t>0.9950,0.0006,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.2918,0.8164,0.0034,0.0040</t>
+  </si>
+  <si>
+    <t>0.9950,0.0013,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.8915,0.1652,0.0024,0.0025</t>
+  </si>
+  <si>
+    <t>0.9809,0.0020,0.0015,0.0108</t>
+  </si>
+  <si>
+    <t>0.5704,0.0033,0.0033,0.5578</t>
+  </si>
+  <si>
+    <t>0.9943,0.0016,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.0169,0.0133,0.9757,0.0121</t>
+  </si>
+  <si>
+    <t>0.9588,0.0030,0.0032,0.0324</t>
+  </si>
+  <si>
+    <t>0.6963,0.0076,0.0153,0.3378</t>
+  </si>
+  <si>
+    <t>0.9456,0.0374,0.0095,0.0042</t>
+  </si>
+  <si>
+    <t>0.8581,0.1170,0.0027,0.0101</t>
+  </si>
+  <si>
+    <t>0.9801,0.0127,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.6215,0.3840,0.0694,0.0238</t>
+  </si>
+  <si>
+    <t>0.9268,0.0283,0.0536,0.0072</t>
+  </si>
+  <si>
+    <t>0.6038,0.5149,0.0120,0.0029</t>
+  </si>
+  <si>
+    <t>0.9951,0.0026,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0011,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9926,0.0007,0.0006,0.0043</t>
+  </si>
+  <si>
+    <t>0.9939,0.0001,0.0001,0.0046</t>
+  </si>
+  <si>
+    <t>0.9936,0.0021,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9917,0.0014,0.0010,0.0027</t>
+  </si>
+  <si>
+    <t>0.9943,0.0006,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9374,0.1465,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.6277,0.5477,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.8943,0.1224,0.0088,0.0044</t>
+  </si>
+  <si>
+    <t>0.0623,0.7853,0.5656,0.0147</t>
+  </si>
+  <si>
+    <t>0.9923,0.0052,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9721,0.0175,0.0037,0.0033</t>
+  </si>
+  <si>
+    <t>0.9844,0.0064,0.0053,0.0026</t>
+  </si>
+  <si>
+    <t>0.9927,0.0065,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.0937,0.9875,0.0062</t>
+  </si>
+  <si>
+    <t>0.9739,0.0337,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0045,0.0245,0.9839,0.0044</t>
+  </si>
+  <si>
+    <t>0.0097,0.3447,0.8828,0.0114</t>
+  </si>
+  <si>
+    <t>0.0444,0.0041,0.9698,0.0004</t>
+  </si>
+  <si>
+    <t>0.1540,0.0481,0.8685,0.0013</t>
+  </si>
+  <si>
+    <t>0.0030,0.0699,0.9831,0.0028</t>
+  </si>
+  <si>
+    <t>0.0115,0.0056,0.9809,0.0015</t>
+  </si>
+  <si>
+    <t>0.0086,0.0252,0.9732,0.0073</t>
+  </si>
+  <si>
+    <t>0.5089,0.0079,0.6004,0.0109</t>
+  </si>
+  <si>
+    <t>0.0865,0.0038,0.9262,0.0020</t>
+  </si>
+  <si>
+    <t>0.2220,0.1163,0.6821,0.0160</t>
+  </si>
+  <si>
+    <t>0.0753,0.5905,0.3429,0.0144</t>
+  </si>
+  <si>
+    <t>0.0654,0.8425,0.1662,0.0052</t>
+  </si>
+  <si>
+    <t>0.5844,0.2585,0.1162,0.0401</t>
+  </si>
+  <si>
+    <t>0.7043,0.0488,0.2682,0.0351</t>
+  </si>
+  <si>
+    <t>0.3471,0.0200,0.7259,0.0057</t>
+  </si>
+  <si>
+    <t>0.9021,0.1961,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9704,0.0606,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9924,0.0054,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0036,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9138,0.1459,0.0031,0.0019</t>
+  </si>
+  <si>
+    <t>0.8670,0.0040,0.2222,0.0007</t>
+  </si>
+  <si>
+    <t>0.9721,0.0013,0.0343,0.0014</t>
+  </si>
+  <si>
+    <t>0.9046,0.0097,0.0227,0.0370</t>
+  </si>
+  <si>
+    <t>0.7690,0.0219,0.2220,0.0178</t>
+  </si>
+  <si>
+    <t>0.7886,0.0019,0.0789,0.0512</t>
+  </si>
+  <si>
+    <t>0.1090,0.0238,0.8234,0.0226</t>
+  </si>
+  <si>
+    <t>0.2632,0.0335,0.7062,0.0279</t>
+  </si>
+  <si>
+    <t>0.3703,0.0484,0.5472,0.1242</t>
+  </si>
+  <si>
+    <t>0.1102,0.0648,0.8555,0.0034</t>
+  </si>
+  <si>
+    <t>0.0041,0.1538,0.7583,0.0197</t>
+  </si>
+  <si>
+    <t>0.9862,0.0035,0.0004,0.0039</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9949,0.0046,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9861,0.0090,0.0028,0.0023</t>
+  </si>
+  <si>
+    <t>0.9935,0.0102,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.0028,0.1609,0.9853,0.0028</t>
+  </si>
+  <si>
+    <t>0.2089,0.7032,0.2645,0.0189</t>
+  </si>
+  <si>
+    <t>0.9739,0.0089,0.0081,0.0028</t>
+  </si>
+  <si>
+    <t>0.0005,0.0019,0.9958,0.0024</t>
+  </si>
+  <si>
+    <t>0.0022,0.0216,0.9108,0.0722</t>
+  </si>
+  <si>
+    <t>0.0120,0.0996,0.9304,0.0208</t>
+  </si>
+  <si>
+    <t>0.0148,0.0043,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.0305,0.0427,0.9377,0.0007</t>
+  </si>
+  <si>
+    <t>0.0055,0.0033,0.9954,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.0105,0.9862,0.0066</t>
+  </si>
+  <si>
+    <t>0.0598,0.1339,0.8311,0.0072</t>
+  </si>
+  <si>
+    <t>0.8598,0.0038,0.0966,0.0285</t>
+  </si>
+  <si>
+    <t>0.7991,0.0012,0.3244,0.0049</t>
+  </si>
+  <si>
+    <t>0.8825,0.0130,0.0811,0.0317</t>
+  </si>
+  <si>
+    <t>0.9926,0.0023,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9933,0.0056,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9965,0.0010,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0018,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9966,0.0019,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0030,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0270,0.0781,0.9249,0.0048</t>
+  </si>
+  <si>
+    <t>0.0129,0.1086,0.9633,0.0022</t>
+  </si>
+  <si>
+    <t>0.0236,0.0956,0.9350,0.0286</t>
+  </si>
+  <si>
+    <t>0.0109,0.0152,0.9729,0.0021</t>
+  </si>
+  <si>
+    <t>0.0280,0.0012,0.9779,0.0028</t>
+  </si>
+  <si>
+    <t>0.0523,0.0749,0.8576,0.1123</t>
+  </si>
+  <si>
+    <t>0.0318,0.0342,0.9477,0.0044</t>
+  </si>
+  <si>
+    <t>0.4421,0.0547,0.4629,0.0492</t>
+  </si>
+  <si>
+    <t>0.5964,0.0004,0.0070,0.4570</t>
+  </si>
+  <si>
+    <t>0.0570,0.0028,0.0043,0.9705</t>
+  </si>
+  <si>
+    <t>0.2016,0.0011,0.0007,0.9331</t>
+  </si>
+  <si>
+    <t>0.0037,0.0002,0.0008,0.9980</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.8756,0.0086,0.0135,0.1178</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4221,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
         <v>426</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
